--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant-n2.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$133</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,6 +468,132 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ObservationType</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -478,10 +604,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Partie narrative</t>
   </si>
   <si>
@@ -631,123 +753,34 @@
     <t>Observation.statusCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.statusCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>Observation.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.effectiveTime</t>
@@ -1502,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK122"/>
+  <dimension ref="A1:AK133"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.1875" customWidth="true" bestFit="true"/>
@@ -3484,7 +3517,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>138</v>
       </c>
@@ -3503,7 +3536,7 @@
         <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>74</v>
@@ -3798,7 +3831,9 @@
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
@@ -3815,10 +3850,12 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3844,13 +3881,11 @@
         <v>74</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
@@ -3868,7 +3903,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3888,16 +3923,18 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E24" s="2"/>
+      <c r="E24" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
@@ -3914,12 +3951,12 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="M24" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3969,7 +4006,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3987,28 +4024,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -4017,11 +4054,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4048,11 +4085,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4070,7 +4109,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4090,17 +4129,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -4118,11 +4157,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4149,11 +4188,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4171,7 +4212,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4191,17 +4232,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -4219,7 +4260,7 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
@@ -4292,7 +4333,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>163</v>
       </c>
@@ -4313,7 +4354,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4322,7 +4363,7 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
@@ -4353,29 +4394,31 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4395,18 +4438,16 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E29" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4423,11 +4464,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4478,7 +4519,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4498,18 +4539,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4526,11 +4565,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4557,11 +4596,13 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4579,7 +4620,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4599,16 +4640,18 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
@@ -4625,10 +4668,12 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
+      <c r="M31" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4654,29 +4699,31 @@
         <v>74</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4696,21 +4743,23 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -4722,17 +4771,13 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L32" t="s" s="2">
         <v>181</v>
       </c>
+      <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>183</v>
-      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>74</v>
@@ -4781,13 +4826,13 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>74</v>
@@ -4801,23 +4846,23 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>74</v>
@@ -4829,11 +4874,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4884,13 +4929,13 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>74</v>
@@ -4904,18 +4949,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E34" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
@@ -4932,12 +4975,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="L34" s="2"/>
-      <c r="M34" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4987,7 +5028,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5007,10 +5048,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5033,14 +5074,12 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5066,11 +5105,13 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -5088,7 +5129,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5108,10 +5149,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5209,17 +5250,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>62</v>
+        <v>194</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5241,7 +5282,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5253,7 +5294,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5268,13 +5309,11 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5292,7 +5331,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5312,23 +5351,23 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
@@ -5340,11 +5379,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5395,7 +5434,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5415,23 +5454,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5443,11 +5482,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5474,13 +5513,11 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5498,7 +5535,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5518,23 +5555,23 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5546,11 +5583,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5601,7 +5638,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5621,23 +5658,23 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>74</v>
@@ -5649,11 +5686,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5680,13 +5717,11 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>74</v>
+        <v>215</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -5704,7 +5739,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5724,10 +5759,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5750,12 +5785,10 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5781,13 +5814,11 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5805,7 +5836,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5825,10 +5856,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5853,11 +5884,15 @@
       <c r="K43" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L43" s="2"/>
+      <c r="L43" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="M43" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>74</v>
@@ -5906,7 +5941,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5926,35 +5961,35 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
@@ -6045,7 +6080,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -6057,11 +6092,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6112,59 +6147,59 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" t="s" s="2">
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6191,13 +6226,11 @@
         <v>74</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>74</v>
@@ -6215,44 +6248,46 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="B47" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6261,13 +6296,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6294,13 +6327,11 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6318,7 +6349,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>239</v>
+        <v>89</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6338,16 +6369,18 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
@@ -6364,10 +6397,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>243</v>
+        <v>85</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6378,7 +6413,7 @@
         <v>74</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>74</v>
+        <v>240</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>74</v>
@@ -6393,11 +6428,13 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6415,7 +6452,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6435,21 +6472,23 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6461,10 +6500,12 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>246</v>
+        <v>112</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
+      <c r="M49" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6514,7 +6555,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>245</v>
+        <v>154</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6534,21 +6575,23 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6560,10 +6603,12 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6589,11 +6634,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>248</v>
+        <v>74</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6611,7 +6658,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6629,26 +6676,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="F51" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -6657,13 +6706,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6714,13 +6761,13 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>249</v>
+        <v>162</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>74</v>
@@ -6734,23 +6781,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6762,11 +6809,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6793,11 +6840,13 @@
         <v>74</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -6815,7 +6864,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6835,18 +6884,16 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
@@ -6863,11 +6910,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6918,7 +6965,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6938,18 +6985,16 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E54" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
@@ -6966,11 +7011,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7021,7 +7066,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7041,23 +7086,23 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -7069,11 +7114,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7124,7 +7169,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7144,23 +7189,23 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -7172,11 +7217,11 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7227,13 +7272,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -7247,23 +7292,23 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>74</v>
@@ -7275,11 +7320,11 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7330,13 +7375,13 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>74</v>
@@ -7348,12 +7393,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7361,13 +7406,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>74</v>
@@ -7376,11 +7421,13 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L58" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="M58" t="s" s="2">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7431,7 +7478,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7451,10 +7498,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7477,12 +7524,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7508,13 +7553,11 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>74</v>
+        <v>255</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7532,7 +7575,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7550,20 +7593,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
@@ -7571,7 +7612,7 @@
         <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>74</v>
@@ -7580,12 +7621,10 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" t="s" s="2">
-        <v>228</v>
-      </c>
+      <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7635,7 +7674,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7655,18 +7694,16 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
@@ -7683,12 +7720,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L61" s="2"/>
-      <c r="M61" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7718,7 +7753,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>88</v>
+        <v>259</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7736,7 +7771,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7754,28 +7789,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>74</v>
@@ -7784,11 +7817,13 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L62" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="M62" t="s" s="2">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7815,11 +7850,13 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -7837,13 +7874,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>74</v>
@@ -7867,7 +7904,7 @@
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
@@ -7885,11 +7922,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7916,13 +7953,11 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7940,7 +7975,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7970,7 +8005,7 @@
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
@@ -7992,7 +8027,7 @@
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8019,11 +8054,13 @@
         <v>74</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8041,7 +8078,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8071,7 +8108,7 @@
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
@@ -8089,11 +8126,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8144,7 +8181,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8174,7 +8211,7 @@
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>80</v>
@@ -8192,11 +8229,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8223,11 +8260,13 @@
         <v>74</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8245,7 +8284,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8274,7 +8313,9 @@
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
@@ -8291,10 +8332,12 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
+      <c r="M67" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8320,11 +8363,13 @@
         <v>74</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>74</v>
@@ -8342,7 +8387,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8371,7 +8416,9 @@
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
@@ -8390,15 +8437,11 @@
       <c r="K68" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>181</v>
-      </c>
+      <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>74</v>
@@ -8447,7 +8490,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8476,11 +8519,9 @@
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" t="s" s="2">
-        <v>186</v>
-      </c>
+      <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>75</v>
@@ -8495,11 +8536,11 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8550,7 +8591,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8579,9 +8620,7 @@
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
@@ -8598,11 +8637,11 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8653,7 +8692,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8671,7 +8710,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>271</v>
       </c>
@@ -8683,16 +8722,16 @@
         <v>74</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>74</v>
@@ -8701,11 +8740,11 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8756,13 +8795,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8786,13 +8825,13 @@
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8804,11 +8843,11 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8835,13 +8874,11 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8859,13 +8896,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>238</v>
+        <v>89</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8877,7 +8914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>273</v>
       </c>
@@ -8888,15 +8925,17 @@
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>74</v>
@@ -8905,13 +8944,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>275</v>
+        <v>195</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8942,7 +8979,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8960,13 +8997,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>273</v>
+        <v>197</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -8980,21 +9017,23 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>74</v>
@@ -9006,10 +9045,12 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9035,11 +9076,13 @@
         <v>74</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>278</v>
+        <v>74</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>74</v>
@@ -9057,13 +9100,13 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>277</v>
+        <v>202</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>74</v>
@@ -9077,21 +9120,23 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -9103,11 +9148,11 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>280</v>
+        <v>205</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9134,13 +9179,11 @@
         <v>74</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>74</v>
@@ -9158,13 +9201,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>279</v>
+        <v>207</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
@@ -9178,16 +9221,18 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
@@ -9204,10 +9249,12 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9257,7 +9304,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>281</v>
+        <v>211</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9277,21 +9324,23 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -9303,10 +9352,12 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>284</v>
+        <v>85</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9332,13 +9383,11 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>74</v>
+        <v>215</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9356,13 +9405,13 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>283</v>
+        <v>216</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>74</v>
@@ -9376,10 +9425,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9390,7 +9439,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9402,7 +9451,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9431,13 +9480,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9455,13 +9502,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9475,10 +9522,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9489,7 +9536,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9501,11 +9548,17 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>74</v>
@@ -9554,13 +9607,13 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>287</v>
+        <v>224</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>74</v>
@@ -9574,21 +9627,23 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9600,10 +9655,12 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>290</v>
+        <v>227</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9653,13 +9710,13 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>74</v>
@@ -9673,21 +9730,23 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E81" s="2"/>
+      <c r="E81" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>74</v>
@@ -9699,10 +9758,12 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>292</v>
+        <v>176</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9752,13 +9813,13 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>291</v>
+        <v>233</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>74</v>
@@ -9770,18 +9831,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E82" s="2"/>
+      <c r="E82" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
@@ -9789,7 +9852,7 @@
         <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>74</v>
@@ -9798,10 +9861,12 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>294</v>
+        <v>181</v>
       </c>
       <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -9851,7 +9916,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>293</v>
+        <v>183</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9871,23 +9936,23 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9899,11 +9964,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9930,11 +9995,13 @@
         <v>74</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>74</v>
@@ -9952,13 +10019,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9970,12 +10037,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9989,7 +10056,7 @@
         <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -9998,11 +10065,13 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L84" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="M84" t="s" s="2">
-        <v>92</v>
+        <v>286</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10029,13 +10098,11 @@
         <v>74</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -10053,7 +10120,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>93</v>
+        <v>284</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10073,10 +10140,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10087,7 +10154,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -10099,12 +10166,10 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>95</v>
+        <v>254</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10130,13 +10195,11 @@
         <v>74</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10154,19 +10217,19 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>97</v>
+        <v>288</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>74</v>
@@ -10174,23 +10237,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E86" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>74</v>
@@ -10202,11 +10263,11 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>86</v>
+        <v>291</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10233,11 +10294,13 @@
         <v>74</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -10255,13 +10318,13 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>74</v>
@@ -10275,18 +10338,16 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
@@ -10303,12 +10364,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>102</v>
+        <v>293</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10358,7 +10417,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10378,23 +10437,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -10406,12 +10463,10 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>295</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10461,13 +10516,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>109</v>
+        <v>294</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10481,23 +10536,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>74</v>
@@ -10509,12 +10562,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>112</v>
+        <v>297</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10522,7 +10573,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>74</v>
@@ -10564,13 +10615,13 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>115</v>
+        <v>296</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>74</v>
@@ -10584,23 +10635,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>74</v>
@@ -10612,12 +10661,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10667,13 +10714,13 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>119</v>
+        <v>298</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>74</v>
@@ -10687,10 +10734,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10713,12 +10760,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -10768,7 +10813,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>122</v>
+        <v>300</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10788,10 +10833,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10799,10 +10844,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>74</v>
@@ -10814,7 +10859,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>85</v>
+        <v>303</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10828,7 +10873,7 @@
         <v>74</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>306</v>
+        <v>74</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>74</v>
@@ -10843,11 +10888,13 @@
         <v>74</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>307</v>
+        <v>74</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>74</v>
@@ -10865,13 +10912,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -10883,12 +10930,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10899,10 +10946,10 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>74</v>
@@ -10911,12 +10958,10 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>107</v>
+        <v>305</v>
       </c>
       <c r="L93" s="2"/>
-      <c r="M93" t="s" s="2">
-        <v>310</v>
-      </c>
+      <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -10927,7 +10972,7 @@
         <v>74</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>311</v>
+        <v>74</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>74</v>
@@ -10966,13 +11011,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>74</v>
@@ -10986,16 +11031,18 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
@@ -11012,16 +11059,16 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>314</v>
+        <v>86</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
-        <v>311</v>
+        <v>74</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
@@ -11043,13 +11090,11 @@
         <v>74</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>74</v>
@@ -11067,7 +11112,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>315</v>
+        <v>89</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11087,10 +11132,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11101,7 +11146,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -11113,10 +11158,12 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
+      <c r="M95" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11166,13 +11213,13 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>317</v>
+        <v>93</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>74</v>
@@ -11186,10 +11233,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11212,10 +11259,12 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>319</v>
+        <v>95</v>
       </c>
       <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11265,7 +11314,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>320</v>
+        <v>97</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11277,7 +11326,7 @@
         <v>74</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>74</v>
@@ -11285,16 +11334,18 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E97" s="2"/>
+      <c r="E97" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
@@ -11311,10 +11362,12 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>322</v>
+        <v>85</v>
       </c>
       <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11340,13 +11393,11 @@
         <v>74</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11364,7 +11415,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>323</v>
+        <v>89</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11384,16 +11435,18 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
@@ -11410,10 +11463,12 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>325</v>
+        <v>102</v>
       </c>
       <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11463,7 +11518,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>326</v>
+        <v>104</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11483,16 +11538,18 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
@@ -11509,10 +11566,12 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11562,7 +11621,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>329</v>
+        <v>109</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11582,18 +11641,20 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F100" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>75</v>
@@ -11608,10 +11669,12 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>331</v>
+        <v>112</v>
       </c>
       <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -11619,7 +11682,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>74</v>
@@ -11661,7 +11724,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11681,18 +11744,20 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>75</v>
@@ -11707,10 +11772,12 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>334</v>
+        <v>102</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -11760,7 +11827,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>335</v>
+        <v>119</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11780,10 +11847,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11794,7 +11861,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>74</v>
@@ -11806,10 +11873,12 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>337</v>
+        <v>95</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -11859,13 +11928,13 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>338</v>
+        <v>122</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>74</v>
@@ -11879,10 +11948,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11890,7 +11959,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>75</v>
@@ -11905,7 +11974,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>340</v>
+        <v>85</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -11919,7 +11988,7 @@
         <v>74</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>74</v>
@@ -11934,13 +12003,11 @@
         <v>74</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -11958,10 +12025,10 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>75</v>
@@ -11978,10 +12045,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12004,10 +12071,12 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>343</v>
+        <v>107</v>
       </c>
       <c r="L104" s="2"/>
-      <c r="M104" s="2"/>
+      <c r="M104" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -12018,7 +12087,7 @@
         <v>74</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>74</v>
@@ -12057,7 +12126,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12077,10 +12146,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12103,14 +12172,16 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>346</v>
+        <v>107</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
+      <c r="M105" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
@@ -12156,7 +12227,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12176,10 +12247,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12202,7 +12273,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>349</v>
+        <v>107</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12255,7 +12326,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12275,10 +12346,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12289,7 +12360,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>74</v>
@@ -12301,7 +12372,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12354,13 +12425,13 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>74</v>
@@ -12374,10 +12445,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12388,7 +12459,7 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>74</v>
@@ -12400,7 +12471,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12453,13 +12524,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12473,10 +12544,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12487,7 +12558,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>74</v>
@@ -12499,7 +12570,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12552,13 +12623,13 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>74</v>
@@ -12572,10 +12643,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12586,7 +12657,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -12598,12 +12669,10 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="L110" s="2"/>
-      <c r="M110" t="s" s="2">
-        <v>359</v>
-      </c>
+      <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -12653,13 +12722,13 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>74</v>
@@ -12673,18 +12742,16 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E111" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
@@ -12701,12 +12768,10 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>85</v>
+        <v>342</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -12732,11 +12797,13 @@
         <v>74</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>74</v>
@@ -12754,7 +12821,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>89</v>
+        <v>343</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12774,10 +12841,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12788,7 +12855,7 @@
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>74</v>
@@ -12800,12 +12867,10 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>91</v>
+        <v>345</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -12855,13 +12920,13 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>93</v>
+        <v>346</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>74</v>
@@ -12875,10 +12940,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12901,12 +12966,10 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>95</v>
+        <v>348</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -12956,7 +13019,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>97</v>
+        <v>349</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -12968,7 +13031,7 @@
         <v>74</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>74</v>
@@ -12976,18 +13039,16 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E114" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
@@ -13004,12 +13065,10 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>85</v>
+        <v>351</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13035,11 +13094,13 @@
         <v>74</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y114" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z114" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>74</v>
@@ -13057,7 +13118,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>89</v>
+        <v>352</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13077,18 +13138,16 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E115" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
@@ -13105,12 +13164,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>102</v>
+        <v>354</v>
       </c>
       <c r="L115" s="2"/>
-      <c r="M115" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13160,7 +13217,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>104</v>
+        <v>355</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13180,18 +13237,16 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
@@ -13208,12 +13263,10 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>107</v>
+        <v>357</v>
       </c>
       <c r="L116" s="2"/>
-      <c r="M116" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -13263,7 +13316,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>109</v>
+        <v>358</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13283,20 +13336,18 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E117" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>75</v>
@@ -13311,12 +13362,10 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>112</v>
+        <v>360</v>
       </c>
       <c r="L117" s="2"/>
-      <c r="M117" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -13324,7 +13373,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>74</v>
@@ -13366,7 +13415,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>115</v>
+        <v>361</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13386,23 +13435,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E118" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>74</v>
@@ -13414,12 +13461,10 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>102</v>
+        <v>363</v>
       </c>
       <c r="L118" s="2"/>
-      <c r="M118" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -13469,13 +13514,13 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>119</v>
+        <v>362</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>74</v>
@@ -13489,10 +13534,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13515,12 +13560,10 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>95</v>
+        <v>365</v>
       </c>
       <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -13570,7 +13613,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>122</v>
+        <v>364</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13590,10 +13633,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13604,7 +13647,7 @@
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>74</v>
@@ -13616,7 +13659,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>85</v>
+        <v>367</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13627,7 +13670,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>370</v>
+        <v>74</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>74</v>
@@ -13645,11 +13688,13 @@
         <v>74</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y120" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z120" t="s" s="2">
-        <v>371</v>
+        <v>74</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>74</v>
@@ -13667,13 +13712,13 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>74</v>
@@ -13687,10 +13732,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13698,10 +13743,10 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>74</v>
@@ -13713,10 +13758,12 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="L121" s="2"/>
-      <c r="M121" s="2"/>
+      <c r="M121" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -13766,13 +13813,13 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>74</v>
@@ -13786,21 +13833,23 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E122" s="2"/>
+      <c r="E122" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>74</v>
@@ -13812,10 +13861,12 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>375</v>
+        <v>85</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
+      <c r="M122" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -13841,13 +13892,11 @@
         <v>74</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>74</v>
@@ -13865,26 +13914,1137 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L123" s="2"/>
+      <c r="M123" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L124" s="2"/>
+      <c r="M124" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AG122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH122" t="s" s="2">
+      <c r="B125" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L125" s="2"/>
+      <c r="M125" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y125" s="2"/>
+      <c r="Z125" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E126" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L126" s="2"/>
+      <c r="M126" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E127" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L127" s="2"/>
+      <c r="M127" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E128" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L128" s="2"/>
+      <c r="M128" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L129" s="2"/>
+      <c r="M129" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G130" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI122" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK122" t="s" s="2">
+      <c r="H130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L130" s="2"/>
+      <c r="M130" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y131" s="2"/>
+      <c r="Z131" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK133" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK122">
+  <autoFilter ref="A1:AK133">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13894,7 +15054,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI121">
+  <conditionalFormatting sqref="A2:AI132">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
